--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/accent_color_pref.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/accent_color_pref.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C2" t="n">
-        <v>60.5</v>
+        <v>58.04</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>14.5</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>11.5</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
     </row>
   </sheetData>
